--- a/survey_templates/043_digital_content_consumption_preference_poll--survey_templates.xlsx
+++ b/survey_templates/043_digital_content_consumption_preference_poll--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How often do you consume digital content?</t>
+          <t>Content Frequency</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What sources do you use to find digital content?</t>
+          <t>Content Source 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What format do you prefer for digital content?</t>
+          <t>Content Format 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How often do you consume digital content?</t>
+          <t>Content Frequency 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
